--- a/labs/lab-6/downloads/Lab_6_Source_to_Slide_Verification.xlsx
+++ b/labs/lab-6/downloads/Lab_6_Source_to_Slide_Verification.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Rdc7953271b4b4b8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="2" r:id="R149fcfee1fec482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="3" r:id="R01ba2b15f65545bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slide Traceability" sheetId="4" r:id="Ree421008e9284cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Impact" sheetId="5" r:id="Rf57a004842074ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Checklist" sheetId="6" r:id="Rf42c255b34bd4ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" r:id="Re5ac198e90dd4ca2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Register" sheetId="2" r:id="R11cc411e32bb4d96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contradictions" sheetId="3" r:id="Rf61279d5af6c452f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Slide Traceability" sheetId="4" r:id="Rdcfbde9b90334cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Impact" sheetId="5" r:id="R7b38199777e84f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Checklist" sheetId="6" r:id="R678e094de332470c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -524,7 +524,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="27" t="str">
-        <x:v>Review all four source files and record claims in Evidence Register.</x:v>
+        <x:v>Use Copilot in Excel Edit mode to write source claims directly into Evidence Register.</x:v>
       </x:c>
       <x:c r="C5" s="23"/>
       <x:c r="D5" s="28" t="str">
@@ -538,7 +538,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="27" t="str">
-        <x:v>Keep conflicting or unsupported items in Contradictions.</x:v>
+        <x:v>Ask Copilot to write conflicting or unsupported items directly into Contradictions.</x:v>
       </x:c>
       <x:c r="C6" s="23"/>
       <x:c r="D6" s="28"/>
@@ -550,7 +550,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="27" t="str">
-        <x:v>After Copilot creates the deck, map every claim to a source in Slide Traceability.</x:v>
+        <x:v>Reference the draft deck and ask Copilot to populate Slide Traceability.</x:v>
       </x:c>
       <x:c r="C7" s="23"/>
       <x:c r="D7" s="28"/>
@@ -562,7 +562,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="27" t="str">
-        <x:v>Record proposed date replacements in Change Impact before applying them.</x:v>
+        <x:v>Ask Copilot to populate Change Impact before applying date replacements.</x:v>
       </x:c>
       <x:c r="C8" s="23"/>
       <x:c r="D8" s="28"/>
@@ -574,7 +574,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="27" t="str">
-        <x:v>Approve only exact replacements; reject unrelated edits.</x:v>
+        <x:v>Review target ranges, then approve only exact replacements; reject unrelated edits.</x:v>
       </x:c>
       <x:c r="C9" s="23"/>
       <x:c r="D9" s="28"/>
